--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -26737,12 +26737,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N156" t="n">
@@ -26815,40 +26815,185 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW156" t="inlineStr">
+      <c r="AW157" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX156" t="inlineStr">
+      <c r="AX157" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY156" t="inlineStr">
+      <c r="AY157" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ156" t="inlineStr">
+      <c r="AZ157" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA156" t="inlineStr">
+      <c r="BA157" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB156" t="inlineStr">
+      <c r="BB157" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC156" t="inlineStr">
+      <c r="BC157" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -26970,7 +27115,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
@@ -26980,7 +27125,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -24436,12 +24436,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24478,6 +24478,9 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
@@ -24514,42 +24517,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24584,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24611,7 +24614,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24659,42 +24662,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24726,12 +24729,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24770,9 +24773,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -24781,77 +24781,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24878,7 +24869,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -24930,98 +24921,18 @@
       <c r="P146" t="n">
         <v>0</v>
       </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN146" t="b">
-        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -25115,17 +25026,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25150,7 +25061,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25164,76 +25075,168 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="R147" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25265,12 +25268,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25309,9 +25312,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -25320,77 +25320,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25408,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -25469,98 +25460,18 @@
       <c r="P149" t="n">
         <v>0</v>
       </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -25654,17 +25565,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25689,7 +25600,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25703,76 +25614,168 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25804,12 +25807,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25848,9 +25851,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -25859,77 +25859,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25956,7 +25947,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -26008,98 +25999,18 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN152" t="b">
-        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -26193,17 +26104,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26228,7 +26139,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26242,76 +26153,168 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="R153" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -26343,12 +26346,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26387,9 +26390,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -26398,77 +26398,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26486,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -26547,98 +26538,18 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
@@ -26732,17 +26643,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26767,7 +26678,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26781,76 +26692,168 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="R156" t="n">
-        <v>0</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -26882,12 +26885,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26912,12 +26915,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N157" t="n">
@@ -26960,40 +26963,579 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW157" t="inlineStr">
+      <c r="AW160" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX157" t="inlineStr">
+      <c r="AX160" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY157" t="inlineStr">
+      <c r="AY160" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ157" t="inlineStr">
+      <c r="AZ160" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA157" t="inlineStr">
+      <c r="BA160" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB157" t="inlineStr">
+      <c r="BB160" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC157" t="inlineStr">
+      <c r="BC160" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -27115,7 +27657,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -27125,7 +27667,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -27145,7 +27687,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -27541,6 +27541,151 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27574,7 +27719,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -27657,7 +27802,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -27667,7 +27812,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -27686,6 +27686,400 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27802,7 +28196,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -27812,7 +28206,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -27832,7 +28226,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -24584,12 +24584,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24662,42 +24662,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24729,12 +24729,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24807,42 +24807,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24874,12 +24874,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24918,9 +24918,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -24929,77 +24926,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25026,7 +25014,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -25078,98 +25066,18 @@
       <c r="P147" t="n">
         <v>0</v>
       </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -25263,17 +25171,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25298,7 +25206,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25312,76 +25220,168 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25413,12 +25413,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25457,9 +25457,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -25468,77 +25465,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25565,7 +25553,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -25617,98 +25605,18 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
-        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -25802,17 +25710,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25837,7 +25745,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25851,76 +25759,168 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25952,12 +25952,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25996,9 +25996,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -26007,77 +26004,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26092,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -26156,98 +26144,18 @@
       <c r="P153" t="n">
         <v>0</v>
       </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -26341,17 +26249,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26376,7 +26284,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26390,76 +26298,168 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -26491,12 +26491,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26535,9 +26535,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -26546,77 +26543,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26643,7 +26631,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -26695,98 +26683,18 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -26880,17 +26788,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26915,7 +26823,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26929,76 +26837,168 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27030,12 +27030,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27074,9 +27074,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -27085,77 +27082,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27182,7 +27170,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -27234,98 +27222,18 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -27419,17 +27327,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27454,12 +27362,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N160" t="n">
@@ -27468,76 +27376,168 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27569,12 +27569,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -27647,42 +27647,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27714,12 +27714,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27758,9 +27758,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -27769,77 +27766,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27866,7 +27854,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -27918,98 +27906,18 @@
       <c r="P163" t="n">
         <v>0</v>
       </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
@@ -28075,6 +27983,782 @@
         </is>
       </c>
       <c r="BC163" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -28113,7 +28797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28880,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -28206,7 +28890,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28226,7 +28910,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -39684,6 +39684,690 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
+      <c r="AT224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
+      <c r="AT227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39717,7 +40401,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -39800,7 +40484,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -39810,7 +40494,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -39830,7 +40514,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -40251,12 +40251,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40281,12 +40281,12 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N227" t="n">
@@ -40329,40 +40329,185 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
+      <c r="AT228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW227" t="inlineStr">
+      <c r="AW228" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX227" t="inlineStr">
+      <c r="AX228" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY227" t="inlineStr">
+      <c r="AY228" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ227" t="inlineStr">
+      <c r="AZ228" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA227" t="inlineStr">
+      <c r="BA228" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB227" t="inlineStr">
+      <c r="BB228" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC227" t="inlineStr">
+      <c r="BC228" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -40484,7 +40629,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
@@ -40494,7 +40639,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1311,6 +1316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1456,6 +1466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1604,6 +1619,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2294,6 +2314,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2984,6 +3009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3674,6 +3704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4364,6 +4399,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4512,6 +4552,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5047,6 +5092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5192,6 +5242,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5882,6 +5937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6572,6 +6632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7262,6 +7327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7952,6 +8022,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8100,6 +8175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8245,6 +8325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8390,6 +8475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9080,6 +9170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9770,6 +9865,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10460,6 +10560,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11150,6 +11255,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11692,6 +11802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11837,6 +11952,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11982,6 +12102,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12278,6 +12403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12968,6 +13098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13658,6 +13793,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14348,6 +14488,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14890,6 +15035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15815,6 +15965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15960,6 +16115,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16256,6 +16416,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16946,6 +17111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17636,6 +17806,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18326,6 +18501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19016,6 +19196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19558,6 +19743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22823,6 +23013,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22968,6 +23163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23258,6 +23458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23942,6 +24147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24626,6 +24836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25310,6 +25525,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25852,6 +26072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29507,6 +29732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29652,6 +29882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29942,6 +30177,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30626,6 +30866,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31310,6 +31555,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31994,6 +32244,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32681,6 +32936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35556,6 +35816,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35701,6 +35966,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38541,6 +38811,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40396,118 +40671,517 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
         <is>
           <t>鼠疫</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="K230" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N228" t="n">
-        <v>0</v>
-      </c>
-      <c r="O228" t="n">
-        <v>0</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0</v>
-      </c>
-      <c r="S228" t="inlineStr">
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO228" t="inlineStr">
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP228" t="inlineStr">
+      <c r="AP230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR228" t="inlineStr">
+      <c r="AR230" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS228" t="inlineStr"/>
-      <c r="AT228" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU228" t="inlineStr">
+      <c r="AS230" t="inlineStr"/>
+      <c r="AT230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV228" t="inlineStr">
+      <c r="AV230" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW228" t="inlineStr">
+      <c r="AW230" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX228" t="inlineStr">
+      <c r="AX230" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY228" t="inlineStr">
+      <c r="AY230" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ228" t="inlineStr">
+      <c r="AZ230" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA228" t="inlineStr">
+      <c r="BA230" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB228" t="inlineStr">
+      <c r="BB230" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC228" t="inlineStr">
+      <c r="BC230" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -40629,7 +41303,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -40639,7 +41313,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -40659,7 +41333,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -41187,6 +41187,151 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
+      <c r="AT231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41220,7 +41365,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -41303,7 +41448,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -41313,7 +41458,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -41332,6 +41332,400 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41448,7 +41842,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -41458,7 +41852,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -41478,7 +41872,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
